--- a/data/trans_orig/P21D_2_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48478</t>
+          <t>44154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214214</t>
+          <t>213330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225870</t>
+          <t>225737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301806</t>
+          <t>301522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329120</t>
+          <t>328497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520174</t>
+          <t>524498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>551625</t>
+          <t>551790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>48305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1089772</t>
+          <t>1090706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1109804</t>
+          <t>1110341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909986</t>
+          <t>909771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925448</t>
+          <t>925706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007789</t>
+          <t>2006141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032103</t>
+          <t>2032857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306106</t>
+          <t>305750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>310116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615940</t>
+          <t>616044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620302</t>
+          <t>620306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>57131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>82590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1619761</t>
+          <t>1620363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1643108</t>
+          <t>1643571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1528216</t>
+          <t>1528585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1559872</t>
+          <t>1560136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3159462</t>
+          <t>3161319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3198023</t>
+          <t>3198749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_2_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Estudios-trans_orig.xlsx
@@ -725,67 +725,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12450</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19731</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16283</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9278</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36253</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>32719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -838,69 +838,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>221334</t>
+          <t>243340</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213330</t>
+          <t>236089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225737</t>
+          <t>247881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>351266</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>343985</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>355613</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>97,77%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>321492</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>301522</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>328497</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>901</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>542826</t>
+          <t>594606</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524498</t>
+          <t>584652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>551790</t>
+          <t>601412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48305</t>
+          <t>64311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1101189</t>
+          <t>936284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1090706</t>
+          <t>923248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1110341</t>
+          <t>945045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>918826</t>
+          <t>959070</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909771</t>
+          <t>947459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925706</t>
+          <t>967186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2020015</t>
+          <t>1895354</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2006141</t>
+          <t>1880718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032857</t>
+          <t>1908912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>308965</t>
+          <t>338910</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305750</t>
+          <t>335977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310116</t>
+          <t>340068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>619148</t>
+          <t>686119</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616044</t>
+          <t>682033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620306</t>
+          <t>687261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,102 +1754,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30086</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53385</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>74096</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>58182</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>92224</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36433</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>61921</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>45160</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>82590</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1867,102 +1867,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1632706</t>
+          <t>1526833</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1620363</t>
+          <t>1513283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1643571</t>
+          <t>1536515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>96,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1649245</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1636415</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1659714</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3728</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>3176078</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>3157950</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3191992</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1549283</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1528585</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1560136</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3728</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3181988</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3161319</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3198749</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
